--- a/sports_forms/045_soccer_registration_form--sports_forms.xlsx
+++ b/sports_forms/045_soccer_registration_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id Hint</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_id_hint</t>
+          <t>form_id_hint_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id Hint 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>output_file_name</t>
+          <t>output_file_name_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Output File Name</t>
+          <t>Output File Name 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1001,_'name':_'adult',_'label':_'adult'}</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1001, 'name': 'Adult', 'label': 'Adult'}</t>
+          <t>Adult</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1002,_'name':_'junior',_'label':_'junior'}</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1002, 'name': 'Junior', 'label': 'Junior'}</t>
+          <t>Junior</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1003,_'name':_'youth',_'label':_'youth'}</t>
+          <t>youth</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1003, 'name': 'Youth', 'label': 'Youth'}</t>
+          <t>Youth</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1004,_'name':_'senior',_'label':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1004, 'name': 'Senior', 'label': 'Senior'}</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1005,_'name':_'goalkeeper',_'label':_'goalkeeper'}</t>
+          <t>goalkeeper</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1005, 'name': 'Goalkeeper', 'label': 'Goalkeeper'}</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1006,_'name':_'defender',_'label':_'defender'}</t>
+          <t>defender</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1006, 'name': 'Defender', 'label': 'Defender'}</t>
+          <t>Defender</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1007,_'name':_'midfielder',_'label':_'midfielder'}</t>
+          <t>midfielder</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1007, 'name': 'Midfielder', 'label': 'Midfielder'}</t>
+          <t>Midfielder</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1008,_'name':_'forward',_'label':_'forward'}</t>
+          <t>forward</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1008, 'name': 'Forward', 'label': 'Forward'}</t>
+          <t>Forward</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1009,_'name':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1009, 'name': 'chatjimmy', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1284,80 +1284,80 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1010,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1010, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1011,_'name':_'sports_forms',_'label':_'sports_forms'}</t>
+          <t>sports_forms</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1011, 'name': 'Sports Forms', 'label': 'Sports Forms'}</t>
+          <t>Sports Forms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1012,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1012, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1013,_'name':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1013, 'name': 'chatjimmy', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1014,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1014, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
